--- a/outputs/analysis.xlsx
+++ b/outputs/analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="63">
   <si>
     <t>event_id</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>comparable_with_other_years</t>
+  </si>
+  <si>
+    <t>E010</t>
+  </si>
+  <si>
+    <t>Entergy Louisiana</t>
+  </si>
+  <si>
+    <t>Hurricane Francine</t>
   </si>
   <si>
     <t>peak_out</t>
@@ -204,16 +213,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -229,7 +230,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -237,30 +238,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,46 +542,46 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -832,22 +815,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -918,29 +901,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1126,6 +1109,190 @@
       </c>
       <c r="G9">
         <v>-0.07124136287824637</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>101605000</v>
+      </c>
+      <c r="F10">
+        <v>94621000</v>
+      </c>
+      <c r="G10">
+        <v>0.07381025353779816</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>30649000</v>
+      </c>
+      <c r="F11">
+        <v>31303000</v>
+      </c>
+      <c r="G11">
+        <v>-0.02089256620771172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>25771000</v>
+      </c>
+      <c r="F12">
+        <v>24328000</v>
+      </c>
+      <c r="G12">
+        <v>0.05931437027293653</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>9309000</v>
+      </c>
+      <c r="F13">
+        <v>6883000</v>
+      </c>
+      <c r="G13">
+        <v>0.3524625889873602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>3227000</v>
+      </c>
+      <c r="F14">
+        <v>2038000</v>
+      </c>
+      <c r="G14">
+        <v>0.5834151128557409</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>11174000</v>
+      </c>
+      <c r="F15">
+        <v>11125000</v>
+      </c>
+      <c r="G15">
+        <v>0.004404494382022472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>4730000</v>
+      </c>
+      <c r="F16">
+        <v>4155000</v>
+      </c>
+      <c r="G16">
+        <v>0.1383874849578821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>6456000</v>
+      </c>
+      <c r="F17">
+        <v>2556000</v>
+      </c>
+      <c r="G17">
+        <v>1.525821596244131</v>
       </c>
     </row>
   </sheetData>
@@ -1135,41 +1302,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1190,10 +1357,10 @@
         <v>1375000</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H2">
         <v>87200000</v>
@@ -1202,7 +1369,7 @@
         <v>63.41818181818182</v>
       </c>
       <c r="K2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1222,10 +1389,10 @@
         <v>560660</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H3">
         <v>39000000</v>
@@ -1234,135 +1401,167 @@
         <v>69.56087468340884</v>
       </c>
       <c r="K3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="E4">
-        <v>91000</v>
+        <v>250000</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4">
-        <v>2437304</v>
+        <v>173314324</v>
       </c>
       <c r="I4">
-        <v>26.78356043956044</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
+        <v>693.257296</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="E5">
-        <v>680000</v>
+        <v>91000</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H5">
-        <v>192922000</v>
+        <v>2437304</v>
       </c>
       <c r="I5">
-        <v>283.7088235294117</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
+        <v>26.78356043956044</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>2024</v>
       </c>
       <c r="E6">
-        <v>250000</v>
+        <v>680000</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H6">
-        <v>107180000</v>
+        <v>192922000</v>
       </c>
       <c r="I6">
-        <v>428.72</v>
+        <v>283.7088235294117</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>2024</v>
       </c>
       <c r="E7">
+        <v>250000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7">
+        <v>107180000</v>
+      </c>
+      <c r="I7">
+        <v>428.72</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>2024</v>
+      </c>
+      <c r="E8">
         <v>2000000</v>
       </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7">
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8">
         <v>876115000</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>438.0575</v>
       </c>
-      <c r="J7" t="s">
-        <v>47</v>
+      <c r="J8" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1376,28 +1575,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" t="s">
         <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>5</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1405,7 +1604,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1419,7 +1618,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1433,7 +1632,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1447,13 +1646,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1461,7 +1660,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>1</v>

--- a/outputs/analysis.xlsx
+++ b/outputs/analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="159">
   <si>
     <t>event_id</t>
   </si>
@@ -80,6 +80,132 @@
     <t>E006</t>
   </si>
   <si>
+    <t>E061</t>
+  </si>
+  <si>
+    <t>E062</t>
+  </si>
+  <si>
+    <t>E063</t>
+  </si>
+  <si>
+    <t>E064</t>
+  </si>
+  <si>
+    <t>E065</t>
+  </si>
+  <si>
+    <t>E066</t>
+  </si>
+  <si>
+    <t>E067</t>
+  </si>
+  <si>
+    <t>E068</t>
+  </si>
+  <si>
+    <t>E069</t>
+  </si>
+  <si>
+    <t>E070</t>
+  </si>
+  <si>
+    <t>E071</t>
+  </si>
+  <si>
+    <t>E072</t>
+  </si>
+  <si>
+    <t>E073</t>
+  </si>
+  <si>
+    <t>E074</t>
+  </si>
+  <si>
+    <t>E075</t>
+  </si>
+  <si>
+    <t>E076</t>
+  </si>
+  <si>
+    <t>E077</t>
+  </si>
+  <si>
+    <t>E078</t>
+  </si>
+  <si>
+    <t>E079</t>
+  </si>
+  <si>
+    <t>E080</t>
+  </si>
+  <si>
+    <t>E081</t>
+  </si>
+  <si>
+    <t>E082</t>
+  </si>
+  <si>
+    <t>E083</t>
+  </si>
+  <si>
+    <t>E084</t>
+  </si>
+  <si>
+    <t>E085</t>
+  </si>
+  <si>
+    <t>E086</t>
+  </si>
+  <si>
+    <t>E136</t>
+  </si>
+  <si>
+    <t>E137</t>
+  </si>
+  <si>
+    <t>E138</t>
+  </si>
+  <si>
+    <t>E139</t>
+  </si>
+  <si>
+    <t>E140</t>
+  </si>
+  <si>
+    <t>E141</t>
+  </si>
+  <si>
+    <t>E142</t>
+  </si>
+  <si>
+    <t>E143</t>
+  </si>
+  <si>
+    <t>E161</t>
+  </si>
+  <si>
+    <t>E162</t>
+  </si>
+  <si>
+    <t>E163</t>
+  </si>
+  <si>
+    <t>E164</t>
+  </si>
+  <si>
+    <t>E165</t>
+  </si>
+  <si>
+    <t>E166</t>
+  </si>
+  <si>
+    <t>E167</t>
+  </si>
+  <si>
+    <t>E168</t>
+  </si>
+  <si>
     <t>Florida Power &amp; Light</t>
   </si>
   <si>
@@ -92,6 +218,18 @@
     <t>Dominion (North Carolina)</t>
   </si>
   <si>
+    <t>National Grid (Narragansett Electric), now Rhode Island Energy</t>
+  </si>
+  <si>
+    <t>National Grid (Massachusetts Electric and Nantucket Electric)</t>
+  </si>
+  <si>
+    <t>LG&amp;E and KU (Louisville Gas and Electric / Kentucky Utilities, combined)</t>
+  </si>
+  <si>
+    <t>Kentucky Power (AEP)</t>
+  </si>
+  <si>
     <t>Hurricane Debby</t>
   </si>
   <si>
@@ -104,6 +242,132 @@
     <t>December 2002 ice storm</t>
   </si>
   <si>
+    <t>March 2010 Flood</t>
+  </si>
+  <si>
+    <t>Hurricane Earl (September 2010)</t>
+  </si>
+  <si>
+    <t>Tropical Storm Irene</t>
+  </si>
+  <si>
+    <t>October 2011 Snowstorm</t>
+  </si>
+  <si>
+    <t>January 2012 Snow/Wind Storm</t>
+  </si>
+  <si>
+    <t>July 2012 Lightning Storm</t>
+  </si>
+  <si>
+    <t>Hurricane Sandy</t>
+  </si>
+  <si>
+    <t>November 2012 Snowstorm</t>
+  </si>
+  <si>
+    <t>February 2013 Nor'easter (Nemo)</t>
+  </si>
+  <si>
+    <t>February 2013 Coastal Storm</t>
+  </si>
+  <si>
+    <t>March 2013 Snowstorm</t>
+  </si>
+  <si>
+    <t>November 1, 2013 Wind Storm</t>
+  </si>
+  <si>
+    <t>January 26, 2015 Nor'easter (Juno)</t>
+  </si>
+  <si>
+    <t>February 14, 2015 Winter Storm (Neptune)</t>
+  </si>
+  <si>
+    <t>August 4, 2015 Lightning Storm</t>
+  </si>
+  <si>
+    <t>February 5, 2016 Winter Storm (Lexi)</t>
+  </si>
+  <si>
+    <t>February 8, 2016 Winter Storm (Mars)</t>
+  </si>
+  <si>
+    <t>April 3, 2016 Wind Storm</t>
+  </si>
+  <si>
+    <t>February 9, 2017 Winter Storm (Niko)</t>
+  </si>
+  <si>
+    <t>March 14, 2017 Winter Storm (Stella)</t>
+  </si>
+  <si>
+    <t>October 29, 2017 Wind/Rain Storm (Philippe)</t>
+  </si>
+  <si>
+    <t>January 20, 2019 Snow/Rain Storm (Harper)</t>
+  </si>
+  <si>
+    <t>February 25, 2019 Wind Storm (Quiana)</t>
+  </si>
+  <si>
+    <t>March 4, 2019 Snowstorm</t>
+  </si>
+  <si>
+    <t>October 16-17, 2019 Wind/Rain Storm</t>
+  </si>
+  <si>
+    <t>October 31, 2019 Wind/Rain Storm</t>
+  </si>
+  <si>
+    <t>January 17, 2022 Wind Storm</t>
+  </si>
+  <si>
+    <t>January 29, 2022 Nor'easter</t>
+  </si>
+  <si>
+    <t>February 24, 2022 Snow Storm</t>
+  </si>
+  <si>
+    <t>July 25, 2022 Heat Storm</t>
+  </si>
+  <si>
+    <t>August 26, 2022 Rain Storm</t>
+  </si>
+  <si>
+    <t>Tropical Storm Nicole (November 12, 2022)</t>
+  </si>
+  <si>
+    <t>December 15, 2022 Snow Storm</t>
+  </si>
+  <si>
+    <t>December 22, 2022 Snow/Rain Storm</t>
+  </si>
+  <si>
+    <t>March 3, 2023 windstorm</t>
+  </si>
+  <si>
+    <t>Hurricane Helene remnants (Sept 27 - Oct 2, 2024)</t>
+  </si>
+  <si>
+    <t>May 16, 2025 storms (EF4 tornado)</t>
+  </si>
+  <si>
+    <t>February 10, 2021 ice storm</t>
+  </si>
+  <si>
+    <t>January 5, 2025 snow and ice storm</t>
+  </si>
+  <si>
+    <t>February 15, 2025 thunderstorm and flooding</t>
+  </si>
+  <si>
+    <t>May 16, 2025 thunderstorm</t>
+  </si>
+  <si>
+    <t>December 18, 2025 thunderstorm</t>
+  </si>
+  <si>
     <t>final_usd_m</t>
   </si>
   <si>
@@ -143,13 +407,10 @@
     <t>comparable_with_other_years</t>
   </si>
   <si>
-    <t>E010</t>
-  </si>
-  <si>
-    <t>Entergy Louisiana</t>
-  </si>
-  <si>
-    <t>Hurricane Francine</t>
+    <t>E130</t>
+  </si>
+  <si>
+    <t>Georgia Power</t>
   </si>
   <si>
     <t>peak_out</t>
@@ -164,16 +425,22 @@
     <t>exact</t>
   </si>
   <si>
+    <t>approximate</t>
+  </si>
+  <si>
     <t>lower_bound</t>
   </si>
   <si>
-    <t>approximate</t>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>approximate customer count</t>
   </si>
   <si>
     <t>customer count is a lower bound, so this is an upper bound</t>
   </si>
   <si>
-    <t>approximate customer count</t>
+    <t>customer count is an upper bound, so this is a lower bound</t>
   </si>
   <si>
     <t>nominal dollars; adjust for inflation before comparing</t>
@@ -191,6 +458,27 @@
     <t>verified_lines</t>
   </si>
   <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>KY</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
     <t>FL</t>
   </si>
   <si>
@@ -200,13 +488,13 @@
     <t>TN</t>
   </si>
   <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>CT</t>
+    <t>NC/SC</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>MI</t>
   </si>
 </sst>
 </file>
@@ -538,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -590,10 +878,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D2">
         <v>2024</v>
@@ -631,10 +919,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>2024</v>
@@ -672,10 +960,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <v>2024</v>
@@ -713,10 +1001,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D5">
         <v>2002</v>
@@ -745,10 +1033,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>2002</v>
@@ -777,10 +1065,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>2002</v>
@@ -802,6 +1090,1614 @@
       </c>
       <c r="N7">
         <v>2.437304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8">
+        <v>2010</v>
+      </c>
+      <c r="E8">
+        <v>0.003523816861779305</v>
+      </c>
+      <c r="F8">
+        <v>0.005055043393261118</v>
+      </c>
+      <c r="G8">
+        <v>0.005262517858120885</v>
+      </c>
+      <c r="H8">
+        <v>0.06444472499654209</v>
+      </c>
+      <c r="I8">
+        <v>0.2322651105927086</v>
+      </c>
+      <c r="J8">
+        <v>0.2247175887289845</v>
+      </c>
+      <c r="M8">
+        <v>0.007748498246910394</v>
+      </c>
+      <c r="N8">
+        <v>2.154482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>2010</v>
+      </c>
+      <c r="E9">
+        <v>0.5247575343919785</v>
+      </c>
+      <c r="F9">
+        <v>0.1946945143159002</v>
+      </c>
+      <c r="G9">
+        <v>0.004622212787175797</v>
+      </c>
+      <c r="H9">
+        <v>0.001323100696355796</v>
+      </c>
+      <c r="I9">
+        <v>0.003331819337511633</v>
+      </c>
+      <c r="J9">
+        <v>0.1334443322661308</v>
+      </c>
+      <c r="M9">
+        <v>0.001050334601304834</v>
+      </c>
+      <c r="N9">
+        <v>0.810218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10">
+        <v>2011</v>
+      </c>
+      <c r="E10">
+        <v>0.5009020597593487</v>
+      </c>
+      <c r="F10">
+        <v>0.133610316847738</v>
+      </c>
+      <c r="G10">
+        <v>0.02835702935894777</v>
+      </c>
+      <c r="H10">
+        <v>0.02251155332268641</v>
+      </c>
+      <c r="I10">
+        <v>0.03066954183427955</v>
+      </c>
+      <c r="J10">
+        <v>0.1251129797124681</v>
+      </c>
+      <c r="M10">
+        <v>0.003053997617783862</v>
+      </c>
+      <c r="N10">
+        <v>35.715483</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11">
+        <v>2011</v>
+      </c>
+      <c r="E11">
+        <v>0.0004844403852670644</v>
+      </c>
+      <c r="F11">
+        <v>0.142271297572398</v>
+      </c>
+      <c r="G11">
+        <v>0.06146210212692025</v>
+      </c>
+      <c r="H11">
+        <v>0.03214758918516188</v>
+      </c>
+      <c r="I11">
+        <v>0.02924525127116687</v>
+      </c>
+      <c r="J11">
+        <v>0.3465548775477142</v>
+      </c>
+      <c r="M11">
+        <v>0.01203431309249055</v>
+      </c>
+      <c r="N11">
+        <v>1.277763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12">
+        <v>2012</v>
+      </c>
+      <c r="E12">
+        <v>0.7475567278381489</v>
+      </c>
+      <c r="F12">
+        <v>0.0594610086705964</v>
+      </c>
+      <c r="G12">
+        <v>0.0122515000043924</v>
+      </c>
+      <c r="H12">
+        <v>0.0005040278302425483</v>
+      </c>
+      <c r="I12">
+        <v>0.009771441497632496</v>
+      </c>
+      <c r="J12">
+        <v>0.07951615524496412</v>
+      </c>
+      <c r="M12">
+        <v>0.001651542171426563</v>
+      </c>
+      <c r="N12">
+        <v>0.910664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13">
+        <v>2012</v>
+      </c>
+      <c r="E13">
+        <v>0.557004413595047</v>
+      </c>
+      <c r="F13">
+        <v>0.06492637632370041</v>
+      </c>
+      <c r="G13">
+        <v>0.0002348698029495733</v>
+      </c>
+      <c r="H13">
+        <v>0.01020616052817237</v>
+      </c>
+      <c r="I13">
+        <v>0.007722679259483981</v>
+      </c>
+      <c r="J13">
+        <v>0.1679643816385193</v>
+      </c>
+      <c r="M13">
+        <v>0.01625405795412388</v>
+      </c>
+      <c r="N13">
+        <v>1.124027</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14">
+        <v>2012</v>
+      </c>
+      <c r="E14">
+        <v>0.4652673327943816</v>
+      </c>
+      <c r="F14">
+        <v>0.1735691447901829</v>
+      </c>
+      <c r="G14">
+        <v>0.04283019447245914</v>
+      </c>
+      <c r="H14">
+        <v>0.01879943701151552</v>
+      </c>
+      <c r="I14">
+        <v>0.0426681057379706</v>
+      </c>
+      <c r="J14">
+        <v>0.1039196281812959</v>
+      </c>
+      <c r="M14">
+        <v>0.006358423092927752</v>
+      </c>
+      <c r="N14">
+        <v>23.807947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <v>2012</v>
+      </c>
+      <c r="E15">
+        <v>0.1693746900618363</v>
+      </c>
+      <c r="F15">
+        <v>0.2519424037262462</v>
+      </c>
+      <c r="G15">
+        <v>0.00822552997323928</v>
+      </c>
+      <c r="H15">
+        <v>0.003970198102571174</v>
+      </c>
+      <c r="I15">
+        <v>0.04364209620779563</v>
+      </c>
+      <c r="J15">
+        <v>0.2367069927281547</v>
+      </c>
+      <c r="M15">
+        <v>0.005789000264206519</v>
+      </c>
+      <c r="N15">
+        <v>2.675937</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16">
+        <v>2013</v>
+      </c>
+      <c r="E16">
+        <v>0.6868513939915361</v>
+      </c>
+      <c r="F16">
+        <v>0.09494039284159674</v>
+      </c>
+      <c r="G16">
+        <v>0.03051153355634097</v>
+      </c>
+      <c r="H16">
+        <v>0.004689624098501578</v>
+      </c>
+      <c r="I16">
+        <v>0.01909968992188461</v>
+      </c>
+      <c r="J16">
+        <v>0.07095477953270782</v>
+      </c>
+      <c r="M16">
+        <v>0.002898116602839858</v>
+      </c>
+      <c r="N16">
+        <v>51.765343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17">
+        <v>2013</v>
+      </c>
+      <c r="E17">
+        <v>0.7998334781084189</v>
+      </c>
+      <c r="F17">
+        <v>0.06500218078926245</v>
+      </c>
+      <c r="G17">
+        <v>0.006038403882171407</v>
+      </c>
+      <c r="H17">
+        <v>0.0001374447014151306</v>
+      </c>
+      <c r="I17">
+        <v>0.003668551797104742</v>
+      </c>
+      <c r="J17">
+        <v>0.06048238814139334</v>
+      </c>
+      <c r="M17">
+        <v>0.0006866126417360304</v>
+      </c>
+      <c r="N17">
+        <v>1.637022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18">
+        <v>2013</v>
+      </c>
+      <c r="E18">
+        <v>0.7188778464284576</v>
+      </c>
+      <c r="F18">
+        <v>0.06530502228288515</v>
+      </c>
+      <c r="G18">
+        <v>0.03847363793140702</v>
+      </c>
+      <c r="H18">
+        <v>0.00089065620340947</v>
+      </c>
+      <c r="I18">
+        <v>0.007292247665415036</v>
+      </c>
+      <c r="J18">
+        <v>0.07865314617345603</v>
+      </c>
+      <c r="M18">
+        <v>0.004562049476098589</v>
+      </c>
+      <c r="N18">
+        <v>2.730571</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19">
+        <v>2013</v>
+      </c>
+      <c r="E19">
+        <v>0.7171693266160982</v>
+      </c>
+      <c r="F19">
+        <v>0.1169956656723005</v>
+      </c>
+      <c r="G19">
+        <v>0.02905222860880154</v>
+      </c>
+      <c r="H19">
+        <v>0.0005093094898669799</v>
+      </c>
+      <c r="I19">
+        <v>0.005751119561402176</v>
+      </c>
+      <c r="J19">
+        <v>0.06189989230143126</v>
+      </c>
+      <c r="M19">
+        <v>0.0009714458872659036</v>
+      </c>
+      <c r="N19">
+        <v>1.250713</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20">
+        <v>2015</v>
+      </c>
+      <c r="E20">
+        <v>0.5601730312295282</v>
+      </c>
+      <c r="F20">
+        <v>0.1249222845984935</v>
+      </c>
+      <c r="G20">
+        <v>0.02641816093689836</v>
+      </c>
+      <c r="H20">
+        <v>0.01257810997534105</v>
+      </c>
+      <c r="I20">
+        <v>0.05819279204338907</v>
+      </c>
+      <c r="J20">
+        <v>0.07874025054986558</v>
+      </c>
+      <c r="M20">
+        <v>0.002042328073229566</v>
+      </c>
+      <c r="N20">
+        <v>7.191303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21">
+        <v>2015</v>
+      </c>
+      <c r="E21">
+        <v>0.3818414598089514</v>
+      </c>
+      <c r="F21">
+        <v>0.09737173396012043</v>
+      </c>
+      <c r="G21">
+        <v>0.02095509410174257</v>
+      </c>
+      <c r="H21">
+        <v>0.0004063082847839872</v>
+      </c>
+      <c r="I21">
+        <v>0.01131666198683822</v>
+      </c>
+      <c r="J21">
+        <v>0.2374202492148116</v>
+      </c>
+      <c r="M21">
+        <v>0.001951581441102034</v>
+      </c>
+      <c r="N21">
+        <v>1.075538</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22">
+        <v>2015</v>
+      </c>
+      <c r="E22">
+        <v>0.5397000164289522</v>
+      </c>
+      <c r="F22">
+        <v>0.09653106544108864</v>
+      </c>
+      <c r="G22">
+        <v>0.040925166242405</v>
+      </c>
+      <c r="H22">
+        <v>0.01802381328348209</v>
+      </c>
+      <c r="I22">
+        <v>0.008366238447370661</v>
+      </c>
+      <c r="J22">
+        <v>0.1361685656774693</v>
+      </c>
+      <c r="M22">
+        <v>0.01575033035439221</v>
+      </c>
+      <c r="N22">
+        <v>12.532753</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23">
+        <v>2016</v>
+      </c>
+      <c r="E23">
+        <v>0.3840829175794842</v>
+      </c>
+      <c r="F23">
+        <v>0.09002966602057159</v>
+      </c>
+      <c r="G23">
+        <v>0.0483105096085821</v>
+      </c>
+      <c r="H23">
+        <v>0.006209219084087915</v>
+      </c>
+      <c r="I23">
+        <v>0.00880124818203575</v>
+      </c>
+      <c r="J23">
+        <v>0.2100853950077978</v>
+      </c>
+      <c r="M23">
+        <v>0.03359440132760702</v>
+      </c>
+      <c r="N23">
+        <v>7.60466</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24">
+        <v>2016</v>
+      </c>
+      <c r="E24">
+        <v>0.4711405703267861</v>
+      </c>
+      <c r="F24">
+        <v>0.1286896088611263</v>
+      </c>
+      <c r="G24">
+        <v>0.002747497779129086</v>
+      </c>
+      <c r="H24">
+        <v>0.002068452375053465</v>
+      </c>
+      <c r="I24">
+        <v>0.007085182737738236</v>
+      </c>
+      <c r="J24">
+        <v>0.1717641980148724</v>
+      </c>
+      <c r="M24">
+        <v>0.03765510915268373</v>
+      </c>
+      <c r="N24">
+        <v>2.522659</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25">
+        <v>2016</v>
+      </c>
+      <c r="E25">
+        <v>0.5985701384048154</v>
+      </c>
+      <c r="F25">
+        <v>0.07265595202083305</v>
+      </c>
+      <c r="G25">
+        <v>0.05201250334284675</v>
+      </c>
+      <c r="H25">
+        <v>0.01403338024278931</v>
+      </c>
+      <c r="I25">
+        <v>0.002207922875593492</v>
+      </c>
+      <c r="J25">
+        <v>0.1283554509226257</v>
+      </c>
+      <c r="M25">
+        <v>0.001601278392277038</v>
+      </c>
+      <c r="N25">
+        <v>0.912396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26">
+        <v>2017</v>
+      </c>
+      <c r="E26">
+        <v>0.3531801079104375</v>
+      </c>
+      <c r="F26">
+        <v>0.1196342036981256</v>
+      </c>
+      <c r="G26">
+        <v>0.006609646411000312</v>
+      </c>
+      <c r="H26">
+        <v>0.005250857417653556</v>
+      </c>
+      <c r="I26">
+        <v>0.007075677346734944</v>
+      </c>
+      <c r="J26">
+        <v>0.2466664420734446</v>
+      </c>
+      <c r="M26">
+        <v>0.007840945722423916</v>
+      </c>
+      <c r="N26">
+        <v>1.513848</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27">
+        <v>2017</v>
+      </c>
+      <c r="E27">
+        <v>0.5340264908104853</v>
+      </c>
+      <c r="F27">
+        <v>0.2094676906273987</v>
+      </c>
+      <c r="G27">
+        <v>0.04907684779104131</v>
+      </c>
+      <c r="H27">
+        <v>0.005466955226176792</v>
+      </c>
+      <c r="I27">
+        <v>0.01673324193554546</v>
+      </c>
+      <c r="J27">
+        <v>0.08280642308592465</v>
+      </c>
+      <c r="M27">
+        <v>0.002882685501957706</v>
+      </c>
+      <c r="N27">
+        <v>3.666026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28">
+        <v>2017</v>
+      </c>
+      <c r="E28">
+        <v>0.4570572346895526</v>
+      </c>
+      <c r="F28">
+        <v>0.1464171045088085</v>
+      </c>
+      <c r="G28">
+        <v>0.03121849697325618</v>
+      </c>
+      <c r="H28">
+        <v>0.01889695672505527</v>
+      </c>
+      <c r="I28">
+        <v>0.02044087630828968</v>
+      </c>
+      <c r="J28">
+        <v>0.1464046259605887</v>
+      </c>
+      <c r="M28">
+        <v>0.01271920256557064</v>
+      </c>
+      <c r="N28">
+        <v>21.196376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29">
+        <v>2019</v>
+      </c>
+      <c r="E29">
+        <v>0.6758028298991304</v>
+      </c>
+      <c r="F29">
+        <v>0.1639752854020337</v>
+      </c>
+      <c r="G29">
+        <v>0.01708895245973431</v>
+      </c>
+      <c r="H29">
+        <v>0.001379006134428431</v>
+      </c>
+      <c r="I29">
+        <v>0.01052426692882385</v>
+      </c>
+      <c r="J29">
+        <v>0.05956791048994033</v>
+      </c>
+      <c r="M29">
+        <v>0.001569571267144816</v>
+      </c>
+      <c r="N29">
+        <v>7.236371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30">
+        <v>2019</v>
+      </c>
+      <c r="E30">
+        <v>0.5322129054636447</v>
+      </c>
+      <c r="F30">
+        <v>0.0894937628116709</v>
+      </c>
+      <c r="G30">
+        <v>0.02948090908774523</v>
+      </c>
+      <c r="H30">
+        <v>0.005864511541089574</v>
+      </c>
+      <c r="I30">
+        <v>0.01580381597829252</v>
+      </c>
+      <c r="J30">
+        <v>0.1529564145070748</v>
+      </c>
+      <c r="M30">
+        <v>0.005427450125114993</v>
+      </c>
+      <c r="N30">
+        <v>3.448028</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31">
+        <v>2019</v>
+      </c>
+      <c r="E31">
+        <v>0.7059005783271505</v>
+      </c>
+      <c r="F31">
+        <v>0.07842653754383005</v>
+      </c>
+      <c r="G31">
+        <v>0.0340566250119528</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0.01040382760565332</v>
+      </c>
+      <c r="J31">
+        <v>0.07939612586314254</v>
+      </c>
+      <c r="M31">
+        <v>0.00201635217947492</v>
+      </c>
+      <c r="N31">
+        <v>2.656282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32">
+        <v>2019</v>
+      </c>
+      <c r="E32">
+        <v>0.3862821149541818</v>
+      </c>
+      <c r="F32">
+        <v>0.149647482857334</v>
+      </c>
+      <c r="G32">
+        <v>0.02687746308012583</v>
+      </c>
+      <c r="H32">
+        <v>0.01456086774757528</v>
+      </c>
+      <c r="I32">
+        <v>0.01911436904263374</v>
+      </c>
+      <c r="J32">
+        <v>0.1892936701252297</v>
+      </c>
+      <c r="M32">
+        <v>0.005815993025056204</v>
+      </c>
+      <c r="N32">
+        <v>5.649938</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33">
+        <v>2019</v>
+      </c>
+      <c r="E33">
+        <v>0.20869846125608</v>
+      </c>
+      <c r="F33">
+        <v>0.1410740004282786</v>
+      </c>
+      <c r="G33">
+        <v>0.01946440698705987</v>
+      </c>
+      <c r="H33">
+        <v>0.01592046254091591</v>
+      </c>
+      <c r="I33">
+        <v>0.03844339074306342</v>
+      </c>
+      <c r="J33">
+        <v>0.2591438098442901</v>
+      </c>
+      <c r="M33">
+        <v>0.01966826761295849</v>
+      </c>
+      <c r="N33">
+        <v>4.086125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>2022</v>
+      </c>
+      <c r="E34">
+        <v>0.510914039191588</v>
+      </c>
+      <c r="F34">
+        <v>0.2958520950160988</v>
+      </c>
+      <c r="G34">
+        <v>0.04596170590488453</v>
+      </c>
+      <c r="H34">
+        <v>0.001672725124738909</v>
+      </c>
+      <c r="I34">
+        <v>0.006751801796954614</v>
+      </c>
+      <c r="J34">
+        <v>0.06573539576571133</v>
+      </c>
+      <c r="M34">
+        <v>0.0006250396373579551</v>
+      </c>
+      <c r="N34">
+        <v>4.367723</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35">
+        <v>2022</v>
+      </c>
+      <c r="E35">
+        <v>0.5197628988391665</v>
+      </c>
+      <c r="F35">
+        <v>0.1693261530396042</v>
+      </c>
+      <c r="G35">
+        <v>0.0480860788533231</v>
+      </c>
+      <c r="H35">
+        <v>0.0007204715163558735</v>
+      </c>
+      <c r="I35">
+        <v>0.02134887108881221</v>
+      </c>
+      <c r="J35">
+        <v>0.1089357577898594</v>
+      </c>
+      <c r="M35">
+        <v>0.001535139994207063</v>
+      </c>
+      <c r="N35">
+        <v>17.006918</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36">
+        <v>2022</v>
+      </c>
+      <c r="E36">
+        <v>0.5611135875461984</v>
+      </c>
+      <c r="F36">
+        <v>0.1836658967947038</v>
+      </c>
+      <c r="G36">
+        <v>0.0566082445694636</v>
+      </c>
+      <c r="H36">
+        <v>0.0009141719304519058</v>
+      </c>
+      <c r="I36">
+        <v>0.007468901009814031</v>
+      </c>
+      <c r="J36">
+        <v>0.0896292613392833</v>
+      </c>
+      <c r="M36">
+        <v>0.003501774460987575</v>
+      </c>
+      <c r="N36">
+        <v>1.633172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37">
+        <v>2022</v>
+      </c>
+      <c r="E37">
+        <v>0.4735308459957446</v>
+      </c>
+      <c r="F37">
+        <v>0.3113605496600816</v>
+      </c>
+      <c r="G37">
+        <v>0.0272234698911766</v>
+      </c>
+      <c r="H37">
+        <v>0.004658757778882584</v>
+      </c>
+      <c r="I37">
+        <v>0.00563522540901636</v>
+      </c>
+      <c r="J37">
+        <v>0.08548246691772433</v>
+      </c>
+      <c r="M37">
+        <v>0.0009909920206332063</v>
+      </c>
+      <c r="N37">
+        <v>2.099916</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38">
+        <v>2022</v>
+      </c>
+      <c r="E38">
+        <v>0.3922959633998689</v>
+      </c>
+      <c r="F38">
+        <v>0.323969878976972</v>
+      </c>
+      <c r="G38">
+        <v>0.03624195400634994</v>
+      </c>
+      <c r="H38">
+        <v>0.00256514183441603</v>
+      </c>
+      <c r="I38">
+        <v>0.006597510650664874</v>
+      </c>
+      <c r="J38">
+        <v>0.1153393328923858</v>
+      </c>
+      <c r="M38">
+        <v>0.001053374696291809</v>
+      </c>
+      <c r="N38">
+        <v>2.694198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39">
+        <v>2022</v>
+      </c>
+      <c r="E39">
+        <v>0.4111513557338307</v>
+      </c>
+      <c r="F39">
+        <v>0.2396965431152683</v>
+      </c>
+      <c r="G39">
+        <v>0.03498912454267408</v>
+      </c>
+      <c r="H39">
+        <v>0.00429738691066443</v>
+      </c>
+      <c r="I39">
+        <v>0.008901618015047389</v>
+      </c>
+      <c r="J39">
+        <v>0.1453367262181375</v>
+      </c>
+      <c r="M39">
+        <v>0.001388901231192725</v>
+      </c>
+      <c r="N39">
+        <v>1.913023</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40">
+        <v>2022</v>
+      </c>
+      <c r="E40">
+        <v>0.4695938944038692</v>
+      </c>
+      <c r="F40">
+        <v>0.2217082889499259</v>
+      </c>
+      <c r="G40">
+        <v>0.05427330447350319</v>
+      </c>
+      <c r="H40">
+        <v>0.004583741591825971</v>
+      </c>
+      <c r="I40">
+        <v>0.004418142995936809</v>
+      </c>
+      <c r="J40">
+        <v>0.1203461113938031</v>
+      </c>
+      <c r="M40">
+        <v>0.0003122618013959859</v>
+      </c>
+      <c r="N40">
+        <v>2.904614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41">
+        <v>2022</v>
+      </c>
+      <c r="E41">
+        <v>0.5075813686324473</v>
+      </c>
+      <c r="F41">
+        <v>0.202327564836209</v>
+      </c>
+      <c r="G41">
+        <v>0.02788548230365588</v>
+      </c>
+      <c r="H41">
+        <v>0.002119501608758557</v>
+      </c>
+      <c r="I41">
+        <v>0.007300386533935088</v>
+      </c>
+      <c r="J41">
+        <v>0.1221702563216653</v>
+      </c>
+      <c r="M41">
+        <v>0.001144796907728519</v>
+      </c>
+      <c r="N41">
+        <v>28.943125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42">
+        <v>2023</v>
+      </c>
+      <c r="E42">
+        <v>0.7636185351323259</v>
+      </c>
+      <c r="H42">
+        <v>0.0489380588421166</v>
+      </c>
+      <c r="I42">
+        <v>0.08320483464152782</v>
+      </c>
+      <c r="J42">
+        <v>0.09340146294250631</v>
+      </c>
+      <c r="M42">
+        <v>0.01083710844152336</v>
+      </c>
+      <c r="N42">
+        <v>73.510476</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43">
+        <v>2024</v>
+      </c>
+      <c r="E43">
+        <v>0.6552387332864774</v>
+      </c>
+      <c r="H43">
+        <v>0.07223157692454477</v>
+      </c>
+      <c r="I43">
+        <v>0.03398599211899142</v>
+      </c>
+      <c r="J43">
+        <v>0.2088679490506754</v>
+      </c>
+      <c r="M43">
+        <v>0.02967574861931101</v>
+      </c>
+      <c r="N43">
+        <v>17.057969</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44">
+        <v>2025</v>
+      </c>
+      <c r="E44">
+        <v>0.7015428874402238</v>
+      </c>
+      <c r="H44">
+        <v>0.1166250699635061</v>
+      </c>
+      <c r="I44">
+        <v>0.05907286196633771</v>
+      </c>
+      <c r="J44">
+        <v>0.1073756161450093</v>
+      </c>
+      <c r="M44">
+        <v>0.01538356448492314</v>
+      </c>
+      <c r="N44">
+        <v>21.827451</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45">
+        <v>2021</v>
+      </c>
+      <c r="E45">
+        <v>0.3161267966945981</v>
+      </c>
+      <c r="F45">
+        <v>0.0627330331447522</v>
+      </c>
+      <c r="G45">
+        <v>0.01663607235952137</v>
+      </c>
+      <c r="H45">
+        <v>0.01269700488917983</v>
+      </c>
+      <c r="I45">
+        <v>0.1571085759808271</v>
+      </c>
+      <c r="J45">
+        <v>0.04425749510372246</v>
+      </c>
+      <c r="K45">
+        <v>0.03773546174028217</v>
+      </c>
+      <c r="L45">
+        <v>0.007853459755931547</v>
+      </c>
+      <c r="M45">
+        <v>0.01602829874740729</v>
+      </c>
+      <c r="N45">
+        <v>76.433065</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46">
+        <v>2025</v>
+      </c>
+      <c r="E46">
+        <v>0.6698994525254022</v>
+      </c>
+      <c r="F46">
+        <v>0.07974549876532219</v>
+      </c>
+      <c r="G46">
+        <v>0.02242791405639109</v>
+      </c>
+      <c r="H46">
+        <v>0.03614718467216118</v>
+      </c>
+      <c r="I46">
+        <v>0.005712532556099871</v>
+      </c>
+      <c r="J46">
+        <v>0.05788754753737925</v>
+      </c>
+      <c r="K46">
+        <v>0.07979175115460607</v>
+      </c>
+      <c r="L46">
+        <v>0.02349679372347828</v>
+      </c>
+      <c r="M46">
+        <v>0.02489132500915986</v>
+      </c>
+      <c r="N46">
+        <v>6.896941</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47">
+        <v>2025</v>
+      </c>
+      <c r="E47">
+        <v>0.3127350337923717</v>
+      </c>
+      <c r="F47">
+        <v>0.1191311289759864</v>
+      </c>
+      <c r="G47">
+        <v>0.0194472579286021</v>
+      </c>
+      <c r="H47">
+        <v>0.04187686898943604</v>
+      </c>
+      <c r="I47">
+        <v>0.004549994145316247</v>
+      </c>
+      <c r="J47">
+        <v>0.06416541632913846</v>
+      </c>
+      <c r="K47">
+        <v>0.08968165022261582</v>
+      </c>
+      <c r="L47">
+        <v>0.01707662037211819</v>
+      </c>
+      <c r="M47">
+        <v>0.01860099545204331</v>
+      </c>
+      <c r="N47">
+        <v>8.343747</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48">
+        <v>2025</v>
+      </c>
+      <c r="E48">
+        <v>0.5543085041093511</v>
+      </c>
+      <c r="F48">
+        <v>0.1807407257729069</v>
+      </c>
+      <c r="G48">
+        <v>0.01562720673541058</v>
+      </c>
+      <c r="H48">
+        <v>0.03747223476773508</v>
+      </c>
+      <c r="I48">
+        <v>0.004150516632698839</v>
+      </c>
+      <c r="J48">
+        <v>0.07130621109293714</v>
+      </c>
+      <c r="K48">
+        <v>0.08351850653628982</v>
+      </c>
+      <c r="L48">
+        <v>0.03361772297257645</v>
+      </c>
+      <c r="M48">
+        <v>0.01925837138009407</v>
+      </c>
+      <c r="N48">
+        <v>4.651951</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49">
+        <v>0.437703036542167</v>
+      </c>
+      <c r="F49">
+        <v>0.1439705209894427</v>
+      </c>
+      <c r="G49">
+        <v>0.02226994675334645</v>
+      </c>
+      <c r="H49">
+        <v>0.03065866687392507</v>
+      </c>
+      <c r="I49">
+        <v>0.0146207767326381</v>
+      </c>
+      <c r="J49">
+        <v>0.09254532545687841</v>
+      </c>
+      <c r="K49">
+        <v>0.1330789649731716</v>
+      </c>
+      <c r="L49">
+        <v>0.07492391121393502</v>
+      </c>
+      <c r="M49">
+        <v>0.05022885046449563</v>
+      </c>
+      <c r="N49">
+        <v>2.097221</v>
       </c>
     </row>
   </sheetData>
@@ -825,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -839,10 +2735,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D2">
         <v>107.18</v>
@@ -859,10 +2755,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>192.922</v>
@@ -879,10 +2775,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <v>876.115</v>
@@ -915,16 +2811,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -932,10 +2828,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -955,10 +2851,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -978,10 +2874,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -1001,10 +2897,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -1024,10 +2920,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -1047,10 +2943,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1070,10 +2966,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1093,10 +2989,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1116,10 +3012,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -1139,10 +3035,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1162,10 +3058,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -1185,10 +3081,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -1208,10 +3104,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
@@ -1231,10 +3127,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1254,10 +3150,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1277,10 +3173,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1302,7 +3198,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1319,25 +3215,25 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="J1" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1345,10 +3241,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D2">
         <v>2002</v>
@@ -1357,10 +3253,10 @@
         <v>1375000</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="H2">
         <v>87200000</v>
@@ -1369,7 +3265,7 @@
         <v>63.41818181818182</v>
       </c>
       <c r="K2" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1377,10 +3273,10 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D3">
         <v>2002</v>
@@ -1389,10 +3285,10 @@
         <v>560660</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="H3">
         <v>39000000</v>
@@ -1401,39 +3297,42 @@
         <v>69.56087468340884</v>
       </c>
       <c r="K3" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="D4">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="E4">
-        <v>250000</v>
+        <v>273000</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="H4">
-        <v>173314324</v>
+        <v>35715483</v>
       </c>
       <c r="I4">
-        <v>693.257296</v>
+        <v>130.8259450549451</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>138</v>
+      </c>
+      <c r="K4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1441,10 +3340,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D5">
         <v>2002</v>
@@ -1453,10 +3352,10 @@
         <v>91000</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="H5">
         <v>2437304</v>
@@ -1465,103 +3364,977 @@
         <v>26.78356043956044</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D6">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="E6">
-        <v>680000</v>
+        <v>39000</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="H6">
-        <v>192922000</v>
+        <v>1277764</v>
       </c>
       <c r="I6">
-        <v>283.7088235294117</v>
+        <v>32.76317948717949</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>138</v>
+      </c>
+      <c r="K6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D7">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="E7">
-        <v>250000</v>
+        <v>34000</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="H7">
-        <v>107180000</v>
+        <v>1124027</v>
       </c>
       <c r="I7">
-        <v>428.72</v>
+        <v>33.05961764705882</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>138</v>
+      </c>
+      <c r="K7" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8">
+        <v>2010</v>
+      </c>
+      <c r="E8">
+        <v>50000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8">
+        <v>2154482</v>
+      </c>
+      <c r="I8">
+        <v>43.08964</v>
+      </c>
+      <c r="J8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9">
+        <v>2017</v>
+      </c>
+      <c r="E9">
+        <v>32129</v>
+      </c>
+      <c r="F9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9">
+        <v>1513849</v>
+      </c>
+      <c r="I9">
+        <v>47.1178374677083</v>
+      </c>
+      <c r="J9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10">
+        <v>2024</v>
+      </c>
+      <c r="E10">
+        <v>224000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10">
+        <v>17057969</v>
+      </c>
+      <c r="I10">
+        <v>76.15164732142857</v>
+      </c>
+      <c r="J10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11">
+        <v>2012</v>
+      </c>
+      <c r="E11">
+        <v>11000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11">
+        <v>910664</v>
+      </c>
+      <c r="I11">
+        <v>82.78763636363637</v>
+      </c>
+      <c r="J11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12">
+        <v>2015</v>
+      </c>
+      <c r="E12">
+        <v>146000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" t="s">
+        <v>135</v>
+      </c>
+      <c r="H12">
+        <v>12532753</v>
+      </c>
+      <c r="I12">
+        <v>85.84077397260273</v>
+      </c>
+      <c r="J12" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13">
+        <v>2022</v>
+      </c>
+      <c r="E13">
+        <v>21264</v>
+      </c>
+      <c r="F13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13">
+        <v>2099916</v>
+      </c>
+      <c r="I13">
+        <v>98.75451467268623</v>
+      </c>
+      <c r="J13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14">
+        <v>2016</v>
+      </c>
+      <c r="E14">
+        <v>8490</v>
+      </c>
+      <c r="F14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14">
+        <v>912394</v>
+      </c>
+      <c r="I14">
+        <v>107.466902237927</v>
+      </c>
+      <c r="J14" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15">
+        <v>2022</v>
+      </c>
+      <c r="E15">
+        <v>14317</v>
+      </c>
+      <c r="F15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15">
+        <v>1633170</v>
+      </c>
+      <c r="I15">
+        <v>114.0720821401132</v>
+      </c>
+      <c r="J15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>2022</v>
+      </c>
+      <c r="E16">
+        <v>36772</v>
+      </c>
+      <c r="F16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16">
+        <v>4367724</v>
+      </c>
+      <c r="I16">
+        <v>118.7785271402154</v>
+      </c>
+      <c r="J16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17">
+        <v>2017</v>
+      </c>
+      <c r="E17">
+        <v>176247</v>
+      </c>
+      <c r="F17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17">
+        <v>21196376</v>
+      </c>
+      <c r="I17">
+        <v>120.2651733079145</v>
+      </c>
+      <c r="J17" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18">
+        <v>2016</v>
+      </c>
+      <c r="E18">
+        <v>62200</v>
+      </c>
+      <c r="F18" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18">
+        <v>7604660</v>
+      </c>
+      <c r="I18">
+        <v>122.2614147909968</v>
+      </c>
+      <c r="J18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19">
+        <v>2012</v>
+      </c>
+      <c r="E19">
+        <v>21200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19">
+        <v>2675937</v>
+      </c>
+      <c r="I19">
+        <v>126.2234433962264</v>
+      </c>
+      <c r="J19" t="s">
+        <v>138</v>
+      </c>
+      <c r="K19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20">
+        <v>2022</v>
+      </c>
+      <c r="E20">
+        <v>21525</v>
+      </c>
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20">
+        <v>2904613</v>
+      </c>
+      <c r="I20">
+        <v>134.9413704994193</v>
+      </c>
+      <c r="J20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21">
+        <v>2012</v>
+      </c>
+      <c r="E21">
+        <v>158521</v>
+      </c>
+      <c r="F21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21">
+        <v>23807947</v>
+      </c>
+      <c r="I21">
+        <v>150.1879687864699</v>
+      </c>
+      <c r="J21" t="s">
+        <v>138</v>
+      </c>
+      <c r="K21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22">
+        <v>2022</v>
+      </c>
+      <c r="E22">
+        <v>11963</v>
+      </c>
+      <c r="F22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22">
+        <v>1913023</v>
+      </c>
+      <c r="I22">
+        <v>159.9116442363955</v>
+      </c>
+      <c r="J22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23">
+        <v>2022</v>
+      </c>
+      <c r="E23">
+        <v>16818</v>
+      </c>
+      <c r="F23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23">
+        <v>2694197</v>
+      </c>
+      <c r="I23">
+        <v>160.1972291592342</v>
+      </c>
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24">
+        <v>2022</v>
+      </c>
+      <c r="E24">
+        <v>163182</v>
+      </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24">
+        <v>28943125</v>
+      </c>
+      <c r="I24">
+        <v>177.3671422093123</v>
+      </c>
+      <c r="J24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25">
+        <v>2023</v>
+      </c>
+      <c r="E25">
+        <v>400000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25">
+        <v>73510476</v>
+      </c>
+      <c r="I25">
+        <v>183.77619</v>
+      </c>
+      <c r="J25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26">
+        <v>2013</v>
+      </c>
+      <c r="E26">
+        <v>6800</v>
+      </c>
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26">
+        <v>1250713</v>
+      </c>
+      <c r="I26">
+        <v>183.9283823529412</v>
+      </c>
+      <c r="J26" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27">
+        <v>2025</v>
+      </c>
+      <c r="E27">
+        <v>114000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27">
+        <v>21827452</v>
+      </c>
+      <c r="I27">
+        <v>191.4688771929825</v>
+      </c>
+      <c r="J27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28">
+        <v>2013</v>
+      </c>
+      <c r="E28">
+        <v>238611</v>
+      </c>
+      <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28">
+        <v>51765343</v>
+      </c>
+      <c r="I28">
+        <v>216.9444954339909</v>
+      </c>
+      <c r="J28" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29">
+        <v>2024</v>
+      </c>
+      <c r="E29">
+        <v>680000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29">
+        <v>192922000</v>
+      </c>
+      <c r="I29">
+        <v>283.7088235294117</v>
+      </c>
+      <c r="J29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30">
+        <v>2024</v>
+      </c>
+      <c r="E30">
+        <v>250000</v>
+      </c>
+      <c r="F30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" t="s">
+        <v>135</v>
+      </c>
+      <c r="H30">
+        <v>107180000</v>
+      </c>
+      <c r="I30">
+        <v>428.72</v>
+      </c>
+      <c r="J30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31">
         <v>2024</v>
       </c>
-      <c r="E8">
+      <c r="E31">
         <v>2000000</v>
       </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8">
+      <c r="F31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31">
         <v>876115000</v>
       </c>
-      <c r="I8">
+      <c r="I31">
         <v>438.0575</v>
       </c>
-      <c r="J8" t="s">
-        <v>50</v>
+      <c r="J31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32">
+        <v>2022</v>
+      </c>
+      <c r="E32">
+        <v>32655</v>
+      </c>
+      <c r="F32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" t="s">
+        <v>135</v>
+      </c>
+      <c r="H32">
+        <v>17006919</v>
+      </c>
+      <c r="I32">
+        <v>520.8059715204409</v>
+      </c>
+      <c r="J32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>2024</v>
+      </c>
+      <c r="E33">
+        <v>1600000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" t="s">
+        <v>135</v>
+      </c>
+      <c r="H33">
+        <v>878401000</v>
+      </c>
+      <c r="I33">
+        <v>549.000625</v>
+      </c>
+      <c r="J33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34">
+        <v>2013</v>
+      </c>
+      <c r="E34">
+        <v>4200</v>
+      </c>
+      <c r="F34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" t="s">
+        <v>137</v>
+      </c>
+      <c r="H34">
+        <v>2730571</v>
+      </c>
+      <c r="I34">
+        <v>650.1359523809524</v>
+      </c>
+      <c r="J34" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1571,32 +4344,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="C2">
-        <v>51</v>
+        <v>362</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1604,13 +4377,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1618,13 +4391,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1632,13 +4405,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1646,13 +4419,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1660,15 +4433,113 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>86</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
     </row>
